--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 2.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 2.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Hotel 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BB2B1F-EA95-413A-9E35-79978C4B77B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45F15C0-5D82-4610-A4A4-A34A54880C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -310,7 +321,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -349,15 +360,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -413,9 +415,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -453,9 +455,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -488,26 +490,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -540,26 +525,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -757,15 +725,15 @@
       <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="26" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="2:11" ht="33" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -809,13 +777,34 @@
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="15"/>
+      <c r="E3" s="16" t="str">
+        <f>_xlfn.XLOOKUP(MID(D3,2,2),$C$13:$C$15,$B$13:$B$15)</f>
+        <v>Luxury</v>
+      </c>
+      <c r="F3" s="16" t="str">
+        <f>LEFT(D3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="15">
+        <f>HLOOKUP(VALUE(RIGHT(D3,1)),$F$11:$I$12,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="15">
+        <f>_xlfn.XLOOKUP(MID(D3,2,2),$C$13:$C$15,$D$13:$D$15)</f>
+        <v>750000</v>
+      </c>
+      <c r="I3" s="15">
+        <f>F3*H3</f>
+        <v>750000</v>
+      </c>
+      <c r="J3" s="17">
+        <f>IF(F3&gt;5,5%,0)</f>
+        <v>0.05</v>
+      </c>
+      <c r="K3" s="15">
+        <f>I3-(I3*J3)</f>
+        <v>712500</v>
+      </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="5">
@@ -827,13 +816,34 @@
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="15"/>
+      <c r="E4" s="16" t="str">
+        <f t="shared" ref="E4:E7" si="0">_xlfn.XLOOKUP(MID(D4,2,2),$C$13:$C$15,$B$13:$B$15)</f>
+        <v>VIP</v>
+      </c>
+      <c r="F4" s="16" t="str">
+        <f t="shared" ref="F4:F7" si="1">LEFT(D4)</f>
+        <v>2</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" ref="G4:G7" si="2">HLOOKUP(VALUE(RIGHT(D4,1)),$F$11:$I$12,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" ref="H4:H7" si="3">_xlfn.XLOOKUP(MID(D4,2,2),$C$13:$C$15,$D$13:$D$15)</f>
+        <v>500000</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" ref="I4:I7" si="4">F4*H4</f>
+        <v>1000000</v>
+      </c>
+      <c r="J4" s="17">
+        <f t="shared" ref="J4:J7" si="5">IF(F4&gt;5,5%,0)</f>
+        <v>0.05</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" ref="K4:K7" si="6">I4-(I4*J4)</f>
+        <v>950000</v>
+      </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="5">
@@ -845,13 +855,34 @@
       <c r="D5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="15"/>
+      <c r="E5" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Luxury</v>
+      </c>
+      <c r="F5" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="2"/>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="3"/>
+        <v>750000</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="4"/>
+        <v>3750000</v>
+      </c>
+      <c r="J5" s="17">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="6"/>
+        <v>3562500</v>
+      </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
@@ -863,13 +894,34 @@
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="15"/>
+      <c r="E6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Economy</v>
+      </c>
+      <c r="F6" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="3"/>
+        <v>250000</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="4"/>
+        <v>1500000</v>
+      </c>
+      <c r="J6" s="17">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="6"/>
+        <v>1425000</v>
+      </c>
     </row>
     <row r="7" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="12">
@@ -881,41 +933,68 @@
       <c r="D7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="19"/>
+      <c r="E7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>VIP</v>
+      </c>
+      <c r="F7" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="3"/>
+        <v>500000</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="4"/>
+        <v>1500000</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="6"/>
+        <v>1425000</v>
+      </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="14"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="14">
+        <f>SUM(K3:K7)</f>
+        <v>8075000</v>
+      </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="15"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="15">
+        <f>AVERAGE(K3:K7)</f>
+        <v>1615000</v>
+      </c>
     </row>
     <row r="10" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
@@ -970,12 +1049,12 @@
         <v>750000</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
@@ -988,13 +1067,13 @@
         <v>500000</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
@@ -1007,11 +1086,11 @@
         <v>250000</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
